--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484255_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484255_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1298</v>
+        <v>5.2685</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4723</v>
+        <v>4.8561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6574</v>
+        <v>0.4123</v>
       </c>
       <c r="G2" t="n">
         <v>3.4086</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2323</v>
+        <v>-0.0936</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.4664</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3149</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3931</v>
+        <v>3.209</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2861</v>
+        <v>3.1381</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.893</v>
+        <v>0.0709</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0427</v>
+        <v>5.5186</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6897</v>
+        <v>2.5785</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6471</v>
+        <v>2.9402</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2635</v>
+        <v>5.0281</v>
       </c>
       <c r="K3" t="n">
-        <v>3.584</v>
+        <v>3.7056</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3206</v>
+        <v>1.3225</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7792</v>
+        <v>0.4905</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1057</v>
+        <v>-1.1271</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6735</v>
+        <v>1.6176</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0026</v>
+        <v>-0.9273</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4997</v>
+        <v>0.0634</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4971</v>
+        <v>-0.9907</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.8242</v>
+        <v>-1.7731</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.3238</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3385</v>
+        <v>2.2477</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4311</v>
+        <v>1.4612</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0926</v>
+        <v>0.7865</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5186</v>
+        <v>2.9004</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5785</v>
+        <v>0.1888</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9402</v>
+        <v>2.7116</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0281</v>
+        <v>2.7445</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7056</v>
+        <v>1.5157</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3225</v>
+        <v>1.2288</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4905</v>
+        <v>0.1559</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1271</v>
+        <v>-1.3269</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6176</v>
+        <v>1.4828</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7977</v>
+        <v>-1.8015</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1541</v>
+        <v>-1.2177</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7731</v>
+        <v>-0.6093</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7731</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4123</v>
+        <v>1.5618</v>
       </c>
       <c r="E5" t="n">
-        <v>0.653</v>
+        <v>2.6182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7593</v>
+        <v>-1.0564</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9004</v>
+        <v>3.0427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1888</v>
+        <v>3.6897</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7116</v>
+        <v>-0.6471</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7445</v>
+        <v>2.2635</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5157</v>
+        <v>3.584</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2288</v>
+        <v>-1.3206</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1559</v>
+        <v>0.7792</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3269</v>
+        <v>0.1057</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4828</v>
+        <v>0.6735</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.6369</v>
+        <v>0.1712</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.392</v>
+        <v>0.8318</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2449</v>
+        <v>-0.6605</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>-2.8242</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0.4996</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8865</v>
+        <v>-3.3238</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6868</v>
+        <v>0.4652</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1767</v>
+        <v>-0.1267</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5101</v>
+        <v>0.5918</v>
       </c>
       <c r="G6" t="n">
         <v>0.6224</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3379</v>
+        <v>0.1162</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5531</v>
+        <v>0.2497</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6642</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1573</v>
+        <v>0.0399</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1788</v>
+        <v>-0.2821</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3361</v>
+        <v>0.322</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3784</v>
+        <v>1.0827</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0432</v>
+        <v>-0.6838</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3352</v>
+        <v>1.7665</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4582</v>
+        <v>1.0371</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1228</v>
+        <v>0.3492</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3354</v>
+        <v>0.6879</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0456</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0795</v>
+        <v>-1.033</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002</v>
+        <v>1.0786</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8678</v>
+        <v>-0.4567</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>-0.3425</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5652</v>
+        <v>-0.1143</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2561</v>
+        <v>0.0061</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6054</v>
+        <v>0.1788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3492</v>
+        <v>-0.1727</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0827</v>
+        <v>1.3784</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6838</v>
+        <v>0.0432</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7665</v>
+        <v>1.3352</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0371</v>
+        <v>1.4582</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3492</v>
+        <v>0.1228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6879</v>
+        <v>1.3354</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0456</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.033</v>
+        <v>-0.0795</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0786</v>
+        <v>-0.0002</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7528</v>
+        <v>-0.7044</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>-0.3026</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.4017</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5344</v>
+        <v>-0.1738</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2985</v>
+        <v>-1.574</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7641</v>
+        <v>1.4003</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0456</v>
+        <v>-2.0879</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7199</v>
+        <v>0.272</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6743</v>
+        <v>-2.3598</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0192</v>
+        <v>-1.3646</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6549</v>
+        <v>1.8035</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>-3.1682</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0648</v>
+        <v>-0.7232</v>
       </c>
       <c r="N9" t="n">
-        <v>0.065</v>
+        <v>-1.5316</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0002</v>
+        <v>0.8083</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1893</v>
+        <v>-0.9018</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3026</v>
+        <v>0.3737</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1133</v>
+        <v>-1.2755</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.988</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6108</v>
+        <v>-0.3533</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0383</v>
+        <v>-1.0358</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4275</v>
+        <v>0.6824</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0879</v>
+        <v>0.0456</v>
       </c>
       <c r="H10" t="n">
-        <v>0.272</v>
+        <v>0.7199</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3598</v>
+        <v>-0.6743</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3646</v>
+        <v>-0.0192</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8035</v>
+        <v>0.6549</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.1682</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7232</v>
+        <v>0.0648</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5316</v>
+        <v>0.065</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8083</v>
+        <v>-0.0002</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3388</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0906</v>
+        <v>-0.0399</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2482</v>
+        <v>0.0316</v>
       </c>
       <c r="V10" t="n">
-        <v>3.988</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.032</v>
+        <v>-0.8238</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5494</v>
+        <v>-1.2866</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5173</v>
+        <v>0.4628</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1773</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2454</v>
+        <v>-0.0371</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2421</v>
+        <v>0.0207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0033</v>
+        <v>-0.0578</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.642</v>
+        <v>-5.9037</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6612</v>
+        <v>-4.0864</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9808</v>
+        <v>-1.8174</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9447</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5568</v>
+        <v>-0.8185</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5147</v>
+        <v>0.0895</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0715</v>
+        <v>-0.9081</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5545</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.727900000000001</v>
+        <v>5.543600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.045199999999999</v>
+        <v>3.860799999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6824</v>
+        <v>1.6825</v>
       </c>
       <c r="G13" t="n">
         <v>10.7895</v>
       </c>
       <c r="H13" t="n">
-        <v>7.4151</v>
+        <v>7.415100000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>3.374499999999999</v>
+        <v>3.3745</v>
       </c>
       <c r="J13" t="n">
         <v>11.4087</v>
@@ -1450,7 +1450,7 @@
         <v>-2.689500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6191</v>
+        <v>-0.6190999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>-6.6831</v>
@@ -1459,7 +1459,7 @@
         <v>6.063800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9302</v>
+        <v>2.930200000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.6972</v>
@@ -1468,13 +1468,13 @@
         <v>15.6274</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.2773</v>
+        <v>-5.4617</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9890999999999995</v>
+        <v>0.8263999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.2881</v>
+        <v>-6.288200000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7145</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7792</v>
+        <v>4.5372</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7373</v>
+        <v>4.253</v>
       </c>
       <c r="F14" t="n">
-        <v>0.042</v>
+        <v>0.2843</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0328</v>
+        <v>0.8183</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1484</v>
+        <v>-1.4206</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.1157</v>
+        <v>2.2388</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2398</v>
+        <v>2.2761</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4889</v>
+        <v>0.5756</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.2491</v>
+        <v>1.7005</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2071</v>
+        <v>-1.4579</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3405</v>
+        <v>-1.9962</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1334</v>
+        <v>0.5383</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4227</v>
+        <v>1.0428</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9084</v>
+        <v>0.7582</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5142</v>
+        <v>0.2846</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>0.3321</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1385</v>
+        <v>3.2733</v>
       </c>
       <c r="E15" t="n">
         <v>2.4467</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6918</v>
+        <v>0.8266</v>
       </c>
       <c r="G15" t="n">
         <v>1.6049</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8694</v>
+        <v>1.0043</v>
       </c>
       <c r="T15" t="n">
         <v>1.2025</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3331</v>
+        <v>-0.1983</v>
       </c>
       <c r="V15" t="n">
         <v>0.6642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.773</v>
+        <v>2.471</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4329</v>
+        <v>1.5808</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3401</v>
+        <v>0.8901</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8183</v>
+        <v>1.402</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4206</v>
+        <v>0.4178</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2388</v>
+        <v>0.9842</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2761</v>
+        <v>1.3515</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5756</v>
+        <v>1.3111</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7005</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4579</v>
+        <v>0.0504</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9962</v>
+        <v>-0.8933</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5383</v>
+        <v>0.9437</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7215</v>
+        <v>0.229</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0619</v>
+        <v>0.2841</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3404</v>
+        <v>-0.0551</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>-0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5462</v>
+        <v>2.4283</v>
       </c>
       <c r="E17" t="n">
-        <v>1.682</v>
+        <v>2.5239</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8643</v>
+        <v>-0.0956</v>
       </c>
       <c r="G17" t="n">
-        <v>1.402</v>
+        <v>1.0328</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4178</v>
+        <v>4.1484</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9842</v>
+        <v>-3.1157</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3515</v>
+        <v>3.2398</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3111</v>
+        <v>6.4889</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-3.2491</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0504</v>
+        <v>-2.2071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8933</v>
+        <v>-2.3405</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9437</v>
+        <v>0.1334</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3043</v>
+        <v>2.0718</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3853</v>
+        <v>1.6951</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.081</v>
+        <v>0.3767</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8266</v>
+        <v>-0.4494</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4103</v>
+        <v>-0.0059</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4163</v>
+        <v>-0.4435</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8924</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0891</v>
+        <v>0.4663</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4842</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5733</v>
+        <v>0.5461</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6093</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7266</v>
+        <v>-1.8295</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9104</v>
+        <v>-3.2026</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1838</v>
+        <v>1.3731</v>
       </c>
       <c r="G19" t="n">
         <v>-6.0577</v>
@@ -1936,13 +1936,13 @@
         <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1711</v>
+        <v>1.0682</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4679</v>
+        <v>1.1757</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2968</v>
+        <v>-0.1075</v>
       </c>
       <c r="V19" t="n">
         <v>2.7693</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0224</v>
+        <v>-2.9407</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8348</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1876</v>
+        <v>-2.1059</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4814</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3224</v>
+        <v>-0.2407</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4594</v>
+        <v>-5.1982</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4466</v>
+        <v>-5.4578</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0127</v>
+        <v>0.2596</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5809</v>
@@ -2092,13 +2092,13 @@
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5754</v>
+        <v>1.8366</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3554</v>
+        <v>1.3442</v>
       </c>
       <c r="U21" t="n">
-        <v>0.22</v>
+        <v>0.4923</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1097</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9298</v>
+        <v>-5.3458</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3792</v>
+        <v>-2.9859</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5506</v>
+        <v>-2.3599</v>
       </c>
       <c r="G22" t="n">
         <v>-2.635</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8893</v>
+        <v>0.4732</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7567</v>
+        <v>0.1501</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1325</v>
+        <v>0.3232</v>
       </c>
       <c r="V22" t="n">
         <v>0.3321</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7279</v>
+        <v>-3.053799999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6824</v>
+        <v>-1.682600000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0452</v>
+        <v>-1.3712</v>
       </c>
       <c r="G23" t="n">
         <v>-10.7894</v>
@@ -2221,7 +2221,7 @@
         <v>-3.3744</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6191000000000015</v>
+        <v>0.6190999999999998</v>
       </c>
       <c r="K23" t="n">
         <v>6.6831</v>
@@ -2248,13 +2248,13 @@
         <v>12.6972</v>
       </c>
       <c r="S23" t="n">
-        <v>7.2774</v>
+        <v>7.9515</v>
       </c>
       <c r="T23" t="n">
-        <v>6.288</v>
+        <v>6.2881</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9892000000000001</v>
+        <v>1.6634</v>
       </c>
       <c r="V23" t="n">
         <v>2.714500000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484255_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484255_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-3.3238</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4652</v>
+        <v>0.914</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1267</v>
+        <v>0.914</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5918</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6224</v>
+        <v>0.914</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1617</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5393</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2878</v>
+        <v>0.914</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9619</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3346</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1998</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1162</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2497</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +985,72 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0399</v>
+        <v>0.4652</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2821</v>
+        <v>-0.1267</v>
       </c>
       <c r="F7" t="n">
-        <v>0.322</v>
+        <v>0.5918</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0827</v>
+        <v>0.6224</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6838</v>
+        <v>1.1617</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7665</v>
+        <v>-0.5393</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0371</v>
+        <v>0.2878</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3492</v>
+        <v>0.9619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6879</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0456</v>
+        <v>0.3346</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.033</v>
+        <v>0.1998</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0786</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4567</v>
+        <v>0.1162</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3425</v>
+        <v>0.2497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1143</v>
+        <v>-0.1335</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9037</v>
+        <v>-0.8741</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0864</v>
+        <v>-1.1961</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8174</v>
+        <v>0.322</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9447</v>
+        <v>0.1687</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.623</v>
+        <v>-0.9908</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3217</v>
+        <v>1.1595</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2225</v>
+        <v>0.1231</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0361</v>
+        <v>0.0422</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1863</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7223</v>
+        <v>0.0456</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5868</v>
+        <v>-1.033</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1354</v>
+        <v>1.0786</v>
       </c>
       <c r="P12" t="n">
         <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8185</v>
+        <v>-0.4567</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0895</v>
+        <v>-0.3425</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9081</v>
+        <v>-0.1143</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.543600000000001</v>
+        <v>-5.9037</v>
       </c>
       <c r="E13" t="n">
-        <v>3.860799999999998</v>
+        <v>-4.0864</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6825</v>
+        <v>-1.8174</v>
       </c>
       <c r="G13" t="n">
-        <v>10.7895</v>
+        <v>-3.9447</v>
       </c>
       <c r="H13" t="n">
-        <v>7.415100000000002</v>
+        <v>-2.623</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3745</v>
+        <v>-1.3217</v>
       </c>
       <c r="J13" t="n">
-        <v>11.4087</v>
+        <v>-2.2225</v>
       </c>
       <c r="K13" t="n">
-        <v>14.0982</v>
+        <v>-1.0361</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.689500000000001</v>
+        <v>-1.1863</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6190999999999998</v>
+        <v>-1.7223</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.6831</v>
+        <v>-1.5868</v>
       </c>
       <c r="O13" t="n">
-        <v>6.063800000000001</v>
+        <v>-0.1354</v>
       </c>
       <c r="P13" t="n">
-        <v>2.930200000000001</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6972</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>15.6274</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.4617</v>
+        <v>-0.8185</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8263999999999999</v>
+        <v>0.0895</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.288200000000001</v>
+        <v>-0.9081</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
       <c r="W13" t="n">
-        <v>4.3229</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.037399999999999</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5372</v>
+        <v>5.543599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.253</v>
+        <v>3.860799999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2843</v>
+        <v>1.6825</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8183</v>
+        <v>10.7895</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4206</v>
+        <v>7.415099999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2388</v>
+        <v>3.374499999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2761</v>
+        <v>11.4087</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5756</v>
+        <v>14.0982</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7005</v>
+        <v>-2.6895</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4579</v>
+        <v>-0.6190999999999995</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9962</v>
+        <v>-6.6831</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5383</v>
+        <v>6.0638</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3441</v>
+        <v>2.9302</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-12.6972</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>15.6274</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0428</v>
+        <v>-5.4617</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7582</v>
+        <v>0.8263999999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2846</v>
+        <v>-6.288200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3321</v>
+        <v>-2.7145</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>4.3229</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8865</v>
-      </c>
+        <v>-7.037399999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2733</v>
+        <v>4.5372</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4467</v>
+        <v>4.253</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8266</v>
+        <v>0.2843</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6049</v>
+        <v>0.8183</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0801</v>
+        <v>-1.4206</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5249</v>
+        <v>2.2388</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1976</v>
+        <v>2.2761</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0762</v>
+        <v>0.5756</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>1.7005</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5927</v>
+        <v>-1.4579</v>
       </c>
       <c r="N15" t="n">
         <v>-1.9962</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4035</v>
+        <v>0.5383</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3441</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0043</v>
+        <v>1.0428</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2025</v>
+        <v>0.7582</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1983</v>
+        <v>0.2846</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.471</v>
+        <v>3.2733</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5808</v>
+        <v>2.4467</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8901</v>
+        <v>0.8266</v>
       </c>
       <c r="G16" t="n">
-        <v>1.402</v>
+        <v>1.6049</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4178</v>
+        <v>1.0801</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9842</v>
+        <v>0.5249</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3515</v>
+        <v>3.1976</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3111</v>
+        <v>3.0762</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0504</v>
+        <v>-1.5927</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8933</v>
+        <v>-1.9962</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9437</v>
+        <v>0.4035</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.229</v>
+        <v>1.0043</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2841</v>
+        <v>1.2025</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0551</v>
+        <v>-0.1983</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3321</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4283</v>
+        <v>2.471</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5239</v>
+        <v>1.5808</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0956</v>
+        <v>0.8901</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0328</v>
+        <v>1.402</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1484</v>
+        <v>0.4178</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1157</v>
+        <v>0.9842</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2398</v>
+        <v>1.3515</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4889</v>
+        <v>1.3111</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.2491</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2071</v>
+        <v>0.0504</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3405</v>
+        <v>-0.8933</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1334</v>
+        <v>0.9437</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0718</v>
+        <v>0.229</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6951</v>
+        <v>0.2841</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3767</v>
+        <v>-0.0551</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8865</v>
+        <v>-0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>-0.0549</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4494</v>
+        <v>2.4283</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0059</v>
+        <v>2.5239</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4435</v>
+        <v>-0.0956</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8924</v>
+        <v>1.0328</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3528</v>
+        <v>4.1484</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5397</v>
+        <v>-3.1157</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2034</v>
+        <v>3.2398</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4707</v>
+        <v>6.4889</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>-3.2491</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6891</v>
+        <v>-2.2071</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8235</v>
+        <v>-2.3405</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1344</v>
+        <v>0.1334</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4663</v>
+        <v>2.0718</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07969999999999999</v>
+        <v>1.6951</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5461</v>
+        <v>0.3767</v>
       </c>
       <c r="V18" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X18" t="n">
         <v>-0.6093</v>
       </c>
-      <c r="W18" t="n">
-        <v>0.2772</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.8865</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8295</v>
+        <v>-0.4494</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2026</v>
+        <v>-0.0059</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3731</v>
+        <v>-0.4435</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.0577</v>
+        <v>-0.8924</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.6286</v>
+        <v>-0.3528</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4291</v>
+        <v>-0.5397</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.53</v>
+        <v>-0.2034</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.4278</v>
+        <v>0.4707</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1022</v>
+        <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5277</v>
+        <v>-0.6891</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2008</v>
+        <v>-0.8235</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6731</v>
+        <v>0.1344</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0682</v>
+        <v>0.4663</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1757</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1075</v>
+        <v>0.5461</v>
       </c>
       <c r="V19" t="n">
-        <v>2.7693</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1052</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9407</v>
+        <v>-1.8295</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8348</v>
+        <v>-3.2026</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1059</v>
+        <v>1.3731</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4814</v>
+        <v>-6.0577</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8475</v>
+        <v>-4.6286</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6338</v>
+        <v>-1.4291</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5927</v>
+        <v>-4.53</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>-2.4278</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.1022</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8887</v>
+        <v>-1.5277</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8885</v>
+        <v>-2.2008</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0002</v>
+        <v>0.6731</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2407</v>
+        <v>1.0682</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>1.1757</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0014</v>
+        <v>-0.1075</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>2.7693</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1982</v>
+        <v>-2.9407</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4578</v>
+        <v>-0.8348</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2596</v>
+        <v>-2.1059</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5809</v>
+        <v>-1.4814</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.272</v>
+        <v>-0.8475</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3089</v>
+        <v>-0.6338</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.0627</v>
+        <v>-0.5927</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.755</v>
+        <v>0.0409</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5182</v>
+        <v>-0.8887</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.517</v>
+        <v>-0.8885</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0012</v>
+        <v>-0.0002</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8366</v>
+        <v>-0.2407</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3442</v>
+        <v>-0.2421</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4923</v>
+        <v>0.0014</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1097</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3458</v>
+        <v>-5.1982</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9859</v>
+        <v>-5.4578</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3599</v>
+        <v>0.2596</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.635</v>
+        <v>-4.5809</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5398</v>
+        <v>-3.272</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0951</v>
+        <v>-1.3089</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0571</v>
+        <v>-3.0627</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0975</v>
+        <v>-1.755</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>-1.3077</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5779</v>
+        <v>-1.5182</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4423</v>
+        <v>-1.517</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1356</v>
+        <v>-0.0012</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.5162</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4732</v>
+        <v>1.8366</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1501</v>
+        <v>1.3442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3232</v>
+        <v>0.4923</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3321</v>
+        <v>-0.1097</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8279</v>
+        <v>0.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-5.3458</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.9859</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.3599</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.635</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.5398</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.0951</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.0571</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.0975</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.5779</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.4423</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.1356</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484255_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-3.053799999999998</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-1.682600000000002</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-1.3712</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-10.7894</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>-7.414999999999999</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-3.3744</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>0.6190999999999998</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>6.6831</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>-6.063800000000001</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-11.4089</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-14.0983</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>2.6894</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-15.6275</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>7.9515</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>6.2881</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1.6634</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>2.714500000000001</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>7.0374</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-4.3228</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
